--- a/bin/Debug/net8.0/Files/RAJDHANI NIGHT.xlsx
+++ b/bin/Debug/net8.0/Files/RAJDHANI NIGHT.xlsx
@@ -38649,13 +38649,13 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="E524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="H524" s="3" t="s">
         <x:v>37</x:v>
